--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_178_Congo_R_of.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_178_Congo_R_of.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rd56272793eb843cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R99c4d3ed3a84403b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R89f4da1a2dc3401b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rb487afd95c8d4063"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R11015b243eb04896"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rebbe4a2941d448db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R33f28ead165d4093"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R8c6228b3694b4298"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R134329a468f74bba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R33e2490645344a0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rc4910c91c6c54642"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R5bac6d2b5556458b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ178CommercialTable" displayName="EEZ178CommercialTable" ref="A1:O8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O8"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ178CommercialTable" displayName="EEZ178CommercialTable" ref="A1:E8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E8"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ178FunctionalTable" displayName="EEZ178FunctionalTable" ref="A1:O17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O17"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ178FunctionalTable" displayName="EEZ178FunctionalTable" ref="A1:E17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E17"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ178ValidationTable" displayName="EEZ178ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ178ValidationTable" displayName="EEZ178ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -4446,7 +4400,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra149d4010f054621"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f556037eab142e4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4456,20 +4410,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -4477,444 +4421,155 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>2762.5795248788</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.2695690600213534</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>186.02403487547713</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>2762.5795248788</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>192.2804244197121</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$57,A2,'Species'!$U$2:$U$57))</x:f>
-        <x:v>531189.9635369022</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.2695690600213534</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>186.02403487547713</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>513906.1898823329</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>17283.77365456929</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.033632156986719</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.033632156986719085</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>25.3274183154</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.36</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>229.08676527677724</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>25.3274183154</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>229.08676527677724</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$57,A3,'Species'!$U$2:$U$57))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>5802.176334686788</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.36</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>229.08676527677724</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>5802.176334686788</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>24843.4398733278</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.2753789110448404</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>188.52932432220587</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>24843.4398733278</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>205.32768180115386</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$57,A4,'Species'!$U$2:$U$57))</x:f>
-        <x:v>5101045.9171567485</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.2753789110448404</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>188.52932432220587</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>4683716.933157838</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>417328.9839989105</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0891020934771865</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.08910209347718641</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>4466.3614927642</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.366080345738392</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>232.31665491507547</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>4466.3614927642</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>263.28916997408885</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$57,A5,'Species'!$U$2:$U$57))</x:f>
-        <x:v>1175944.6102341188</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.366080345738392</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>232.31665491507547</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>1037610.161640482</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>138334.44859363674</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.1333202523527017</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.13332025235270178</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>9853.3743219841</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.8493553053038028</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>706.8956437132789</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>9853.3743219841</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1116.4762927357883</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$57,A6,'Species'!$U$2:$U$57))</x:f>
-        <x:v>11001058.83394682</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.8493553053038028</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>706.8956437132789</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>6965307.384086844</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>4035751.449859977</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.5794075160387293</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.5794075160387292</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>1255.780456148</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.9543678888608085</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>900.2598646174239</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>1255.780456148</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1216.0695196908227</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$57,A7,'Species'!$U$2:$U$57))</x:f>
-        <x:v>1527116.3361450206</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.9543678888608085</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>900.2598646174239</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>1130528.7434410052</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>396587.5927040153</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.3507983277779532</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.3507983277779532</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>237.51791673120002</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.4317937953828</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>2702.6748194732672</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>237.51791673120002</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>2734.541965754669</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$57,A8,'Species'!$U$2:$U$57))</x:f>
-        <x:v>649502.7109200895</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.4317937953828</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>2702.6748194732672</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>641933.6927231625</x:v>
       </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>7569.018196927034</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0117909657690942</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.011790965769094186</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G8">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O8">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd708ce2983404f91"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36ec4936c0af4fff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4924,20 +4579,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -4945,930 +4590,326 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>75</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.7651999999999997</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>582.3713479437508</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>592.8441898920086</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$57,A2,'Species'!$U$2:$U$57))</x:f>
-        <x:v>44463.31424190064</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.7651999999999997</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>582.3713479437508</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>43677.85109578131</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>785.4631461193276</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0179830995896955</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.017983099589695534</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>3199.4262736542</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.317857910159722</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2079.0163758238778</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>3199.4262736542</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2248.732390931498</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$57,A3,'Species'!$U$2:$U$57))</x:f>
-        <x:v>7194653.493963462</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.317857910159722</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2079.0163758238778</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>6651659.616168249</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>542993.8777952129</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.081632841896382</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.08163284189638219</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>1460.830504502</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.798584158094559</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>628.9037120104201</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>1460.830504502</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>632.4639102546575</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$57,A4,'Species'!$U$2:$U$57))</x:f>
-        <x:v>923922.573096619</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.798584158094559</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>628.9037120104201</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>918721.7268993625</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>5200.846197256469</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0056609591838097</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.005660959183809718</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>175.63093158549998</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.408806719305319</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2563.3429790179002</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>175.63093158549998</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2565.256130380844</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$57,A5,'Species'!$U$2:$U$57))</x:f>
-        <x:v>450538.32393420243</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.408806719305319</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2563.3429790179002</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>450202.3153780645</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>336.0085561379092</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0007463501289542</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.0007463501289542251</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>398</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.38</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>239.88329190194898</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>398</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>239.88329190194898</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$57,A6,'Species'!$U$2:$U$57))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>95473.5501769757</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.38</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>239.88329190194898</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>95473.5501769757</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>854.3857779786</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.2225400131804065</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>1669.3216009897578</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>854.3857779786</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1673.1328232393873</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$57,A7,'Species'!$U$2:$U$57))</x:f>
-        <x:v>1429500.8888449154</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.2225400131804065</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>1669.3216009897578</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>1426244.6347581164</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>3256.2540867989883</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0022830964670737</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.002283096467073639</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>6.899000000000001e-7</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.08</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1202.2644346174131</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>6.899000000000001e-7</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$57,A8,'Species'!$U$2:$U$57))</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>0.0008294422334425534</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.08</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
-        <x:v>0.0008294422334425534</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>1930.6358087490999</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.6586864748867867</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>455.7078133849692</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>1930.6358087490999</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>490.2684570535334</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$57,A9,'Species'!$U$2:$U$57))</x:f>
-        <x:v>946529.8390877218</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.6586864748867867</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>455.7078133849692</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>879805.8228477739</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>66724.01623994787</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0758394801525344</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.07583948015253432</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>4832.7242136493005</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.3361410917688548</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>216.84084538397337</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>4832.7242136493005</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>225.3162122526044</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$57,A10,'Species'!$U$2:$U$57))</x:f>
-        <x:v>1088891.1146809065</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.3361410917688548</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>216.84084538397337</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>1047932.0039953123</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>40959.11068559426</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0390856568264304</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.0390856568264304</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>10642.861659793802</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.169122458961955</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>147.61227001355476</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>10642.861659793802</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>216.0608620434636</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$57,A11,'Species'!$U$2:$U$57))</x:f>
-        <x:v>2299505.8648243765</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.169122458961955</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>147.61227001355476</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>1571016.9690423922</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>728488.8957819843</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.4637053005391991</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.4637053005391992</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>764.6775680169001</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.7081157102711195</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>510.64103334515045</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>764.6775680169001</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>894.9077234978013</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$57,A12,'Species'!$U$2:$U$57))</x:f>
-        <x:v>684315.8616038391</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.7081157102711195</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>510.64103334515045</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>390475.7435080064</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>293840.1180958327</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.7525182369998042</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.7525182369998041</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>2762.5795248788</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.2695690600213534</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>186.02403487547713</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>2762.5795248788</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>192.2804244197121</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$57,A13,'Species'!$U$2:$U$57))</x:f>
-        <x:v>531189.9635369022</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.2695690600213534</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>186.02403487547713</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>513906.1898823329</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>17283.77365456929</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.033632156986719</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.033632156986719085</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>1576.4176111524998</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.4201678634464283</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>263.12848392393</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>1576.4176111524998</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>433.21667822056975</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$57,A14,'Species'!$U$2:$U$57))</x:f>
-        <x:v>682930.4009918917</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.4201678634464283</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>263.12848392393</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>414800.3760535407</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>268130.02493835107</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.64640738152017</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.6464073815201701</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>14742.489033014099</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.3797015280574576</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>239.71848705760564</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>14742.489033014099</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>244.9926384150738</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$57,A15,'Species'!$U$2:$U$57))</x:f>
-        <x:v>3611801.285003414</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.3797015280574576</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>239.71848705760564</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>3534047.1664574835</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>77754.11854593037</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0220014376955446</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.02200143769554463</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>25.3274183154</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.36</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>229.08676527677724</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>25.3274183154</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>229.08676527677724</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$57,A16,'Species'!$U$2:$U$57))</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>5802.176334686788</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.36</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>229.08676527677724</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
-        <x:v>5802.176334686788</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>3.3946781693999997</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.8</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>630.957344480193</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>3.3946781693999997</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>630.9573444801931</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$57,A17,'Species'!$U$2:$U$57))</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>2141.897123129507</x:v>
       </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.8</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>630.957344480193</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
-        <x:v>2141.897123129507</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G17">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O17">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3921e32221de4ec9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcfd8c6e8b460418f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6043,7 +5084,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -6142,7 +5183,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>19991660.548274383</x:v>
+        <x:v>14978805.28126635</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6156,7 +5197,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>19991660.548274383</x:v>
+        <x:v>17945908.04055065</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6170,7 +5211,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-3.725290298461914e-9</x:v>
+        <x:v>-5012855.267008036</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6184,7 +5225,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-3.725290298461914e-9</x:v>
+        <x:v>-2045752.5077237375</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6195,9 +5236,9 @@
         <x:v>EEZ_178</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -6209,47 +5250,19 @@
         <x:v>EEZ_178</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_178</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_178</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70ead7a901e34ddf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e0175c1f8ad4ca9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6296,7 +5309,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
